--- a/class_diagram/model/entity/成績管理sys_クラス図_model_entity.xlsx
+++ b/class_diagram/model/entity/成績管理sys_クラス図_model_entity.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="117" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{856FC9EA-B95A-4455-B312-B81EACD71F9B}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3022FE9E-84EF-44D6-95AD-2ACE0783C125}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manager" sheetId="1" r:id="rId1"/>
     <sheet name="Major" sheetId="2" r:id="rId2"/>
+    <sheet name="Subject" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -4086,6 +4087,1258 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>classes : List&lt;Class&gt;</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4875AC2-D2A3-4076-8C8B-BB0AFF273A36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="11096625" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Subject</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9796C346-C39C-435F-94FB-6562C4A2B71A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F4875AC2-D2A3-4076-8C8B-BB0AFF273A36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1666875" y="2619375"/>
+          <a:ext cx="1457325" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>id : int</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B31EB45D-0E8F-4FB5-80DE-723672068A84}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9796C346-C39C-435F-94FB-6562C4A2B71A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3295650" y="2619375"/>
+          <a:ext cx="1457325" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>name : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56B6A8EC-1CA4-4AE4-84F5-89788419BB12}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B31EB45D-0E8F-4FB5-80DE-723672068A84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4886325" y="2609850"/>
+          <a:ext cx="1457325" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>kana : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="四角形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{574E905B-79F5-4F09-86FF-AA524F9057F5}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{56B6A8EC-1CA4-4AE4-84F5-89788419BB12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1695450" y="3200400"/>
+          <a:ext cx="2200275" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>manager : Manager</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="四角形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63908341-549E-4527-8B9C-90403011951F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{574E905B-79F5-4F09-86FF-AA524F9057F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4048125" y="3181350"/>
+          <a:ext cx="2400300" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>createdAt : LocalDateTime</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>197303</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="四角形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DE43C5D-DCA4-46CA-8CAE-C2AA628C2E37}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{63908341-549E-4527-8B9C-90403011951F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6600825" y="3181350"/>
+          <a:ext cx="2400299" cy="416378"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>updatedAt : LocalDateTime</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DE6D167-94F5-46F0-A58A-88A30F19329B}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{0DE43C5D-DCA4-46CA-8CAE-C2AA628C2E37}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6543675" y="2600325"/>
+          <a:ext cx="3409950" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>classSubjects : List&lt;ClassSubject&gt;</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4451,4 +5704,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1287867-2093-4047-BDFD-C21A474F6B4F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/class_diagram/model/entity/成績管理sys_クラス図_model_entity.xlsx
+++ b/class_diagram/model/entity/成績管理sys_クラス図_model_entity.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="122" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3022FE9E-84EF-44D6-95AD-2ACE0783C125}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F38C5C4E-2E3A-493D-B8B8-0CE4831BD48C}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manager" sheetId="1" r:id="rId1"/>
     <sheet name="Major" sheetId="2" r:id="rId2"/>
     <sheet name="Subject" sheetId="3" r:id="rId3"/>
+    <sheet name="ClassEntity" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -5339,6 +5340,1091 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>classSubjects : List&lt;ClassSubject&gt;</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB8F4DCA-A56B-403D-AAA0-7BE0A878B244}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="11096625" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassEntity</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EA320EB-0158-44DA-B36D-CDDDE91926AE}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EB8F4DCA-A56B-403D-AAA0-7BE0A878B244}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1666875" y="2619375"/>
+          <a:ext cx="1457325" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>id : int</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4028A867-D5A0-4959-A8AE-CCE63FB9FE31}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4EA320EB-0158-44DA-B36D-CDDDE91926AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3295650" y="2619375"/>
+          <a:ext cx="2409825" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>startYear : int</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="四角形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED0FE53E-4BE3-492D-B64A-E0E72C2D305C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5D8DB8F5-32BB-48B2-B77E-037DD7A87317}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1695450" y="3200400"/>
+          <a:ext cx="2200275" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>manager : Manager</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="四角形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDE0303C-2BA9-4779-B256-784975BB45B8}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{ED0FE53E-4BE3-492D-B64A-E0E72C2D305C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4048125" y="3181350"/>
+          <a:ext cx="2400300" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>createdAt : LocalDateTime</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>197303</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="四角形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5B8BCC0-FBE7-4EF9-BBE6-7055575F9D30}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EDE0303C-2BA9-4779-B256-784975BB45B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6600825" y="3181350"/>
+          <a:ext cx="2400299" cy="416378"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>updatedAt : LocalDateTime</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E764E7B0-B48E-49E6-927E-955C785BB4A2}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E5B8BCC0-FBE7-4EF9-BBE6-7055575F9D30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6543675" y="2600325"/>
+          <a:ext cx="3409950" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>major : Major</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -5714,4 +6800,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A41D728-62A1-45E3-9D7B-91B2201B1CF8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/class_diagram/model/entity/成績管理sys_クラス図_model_entity.xlsx
+++ b/class_diagram/model/entity/成績管理sys_クラス図_model_entity.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29622"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="131" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F38C5C4E-2E3A-493D-B8B8-0CE4831BD48C}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93CB1194-2B28-4CDF-B357-D3E8DF56A17E}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manager" sheetId="1" r:id="rId1"/>
@@ -6425,6 +6425,173 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>major : Major</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8E5A215-1B6C-4B8F-A251-13F3D9FFC44C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E764E7B0-B48E-49E6-927E-955C785BB4A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6115050" y="1781175"/>
+          <a:ext cx="3409950" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>classSubjects : List&lt;ClassSubject&gt;</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>

--- a/class_diagram/model/entity/成績管理sys_クラス図_model_entity.xlsx
+++ b/class_diagram/model/entity/成績管理sys_クラス図_model_entity.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29622"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="134" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93CB1194-2B28-4CDF-B357-D3E8DF56A17E}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C48DC638-A922-4E5B-AA85-6BCC0D00E528}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,8 @@
     <sheet name="Manager" sheetId="1" r:id="rId1"/>
     <sheet name="Major" sheetId="2" r:id="rId2"/>
     <sheet name="Subject" sheetId="3" r:id="rId3"/>
-    <sheet name="ClassEntity" sheetId="4" r:id="rId4"/>
+    <sheet name="ClassSubject" sheetId="5" r:id="rId4"/>
+    <sheet name="ClassEntity" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -5350,6 +5351,1091 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45FA6FA6-0B7A-44BA-810A-33552E9A2471}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="11096625" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassSubject</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5E7B612-3FF0-41BD-AE76-AA8BC2768D23}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{45FA6FA6-0B7A-44BA-810A-33552E9A2471}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1666875" y="2619375"/>
+          <a:ext cx="1457325" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>id : int</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21B47083-71C6-4ACC-A42E-1A178807C601}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B5E7B612-3FF0-41BD-AE76-AA8BC2768D23}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3295650" y="2619375"/>
+          <a:ext cx="2409825" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>classEntity : ClassEntity</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50E4A35A-BB6E-49C0-AA8D-A70F1CF3F7F7}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{21B47083-71C6-4ACC-A42E-1A178807C601}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1695450" y="3200400"/>
+          <a:ext cx="2200275" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>manager : Manager</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="四角形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36A82ED0-3D32-4768-BFE3-6996A8FF4C85}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{50E4A35A-BB6E-49C0-AA8D-A70F1CF3F7F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4048125" y="3181350"/>
+          <a:ext cx="2400300" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>createdAt : LocalDateTime</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>197303</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="四角形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5476B7EC-5237-419E-B806-01048606AA8B}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{36A82ED0-3D32-4768-BFE3-6996A8FF4C85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6600825" y="3181350"/>
+          <a:ext cx="2400299" cy="416378"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>updatedAt : LocalDateTime</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F52860CF-3FFE-4B84-8DBC-494760B096A9}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5476B7EC-5237-419E-B806-01048606AA8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6543675" y="2600325"/>
+          <a:ext cx="3409950" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subject : Subject</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -6970,6 +8056,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055E76BC-C755-4FA2-AEA2-4545D3ADB25B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A41D728-62A1-45E3-9D7B-91B2201B1CF8}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
